--- a/research/traditional_assets/database/data/hong_kong/hong_kong_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0423</v>
+        <v>-0.01735</v>
       </c>
       <c r="E2">
-        <v>-0.0395</v>
+        <v>-0.1175</v>
       </c>
       <c r="F2">
-        <v>0.08439999999999999</v>
+        <v>0.163</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>6341.2</v>
+        <v>2153.8</v>
       </c>
       <c r="L2">
-        <v>0.4719208156582571</v>
+        <v>0.3539872460719217</v>
       </c>
       <c r="M2">
-        <v>5660.7</v>
+        <v>2562.2</v>
       </c>
       <c r="N2">
-        <v>0.07448759921679264</v>
+        <v>0.06957263147033348</v>
       </c>
       <c r="O2">
-        <v>0.8926859269538888</v>
+        <v>1.189618348964621</v>
       </c>
       <c r="P2">
-        <v>5011.7</v>
+        <v>1690.4</v>
       </c>
       <c r="Q2">
-        <v>0.06594758616333664</v>
+        <v>0.04590023270527347</v>
       </c>
       <c r="R2">
-        <v>0.7903393679429761</v>
+        <v>0.7848453895440617</v>
       </c>
       <c r="S2">
-        <v>649</v>
+        <v>871.8000000000001</v>
       </c>
       <c r="T2">
-        <v>0.1146501316091649</v>
+        <v>0.3402544688158614</v>
       </c>
       <c r="U2">
-        <v>75375.5</v>
+        <v>27696.1</v>
       </c>
       <c r="V2">
-        <v>0.991845537612902</v>
+        <v>0.7520453354404428</v>
       </c>
       <c r="W2">
-        <v>0.0590252807434862</v>
+        <v>0.04783149962142175</v>
       </c>
       <c r="X2">
-        <v>0.05763587432871833</v>
+        <v>0.08925402230535204</v>
       </c>
       <c r="Y2">
-        <v>0.001389406414767869</v>
+        <v>-0.04142252268393029</v>
       </c>
       <c r="Z2">
-        <v>0.3001434040823255</v>
+        <v>0.1640331603423873</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04396981268683946</v>
+        <v>0.0704118025188156</v>
       </c>
       <c r="AC2">
-        <v>-0.04396981268683946</v>
+        <v>-0.0704118025188156</v>
       </c>
       <c r="AD2">
-        <v>17519.1</v>
+        <v>11201.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>17519.1</v>
+        <v>11201.5</v>
       </c>
       <c r="AG2">
-        <v>-57856.4</v>
+        <v>-16494.6</v>
       </c>
       <c r="AH2">
-        <v>0.1873414012616252</v>
+        <v>0.2332227061870695</v>
       </c>
       <c r="AI2">
-        <v>0.1651871038063817</v>
+        <v>0.1978340077038963</v>
       </c>
       <c r="AJ2">
-        <v>-3.189648708845128</v>
+        <v>-0.8112191451377307</v>
       </c>
       <c r="AK2">
-        <v>-1.885764945926742</v>
+        <v>-0.5702619915227868</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BOC Hong Kong (Holdings) Limited (SEHK:2388)</t>
+          <t>Hang Seng Bank Limited (SEHK:11)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.04269999999999999</v>
+        <v>-0.0355</v>
       </c>
       <c r="E3">
-        <v>-0.149</v>
+        <v>-0.113</v>
       </c>
       <c r="F3">
-        <v>0.052</v>
+        <v>0.17</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3248.7</v>
+        <v>1261.2</v>
       </c>
       <c r="L3">
-        <v>0.5228454172366621</v>
+        <v>0.3924326342647333</v>
       </c>
       <c r="M3">
-        <v>3218.5</v>
+        <v>1234.9</v>
       </c>
       <c r="N3">
-        <v>0.09290584424956556</v>
+        <v>0.03880136491318473</v>
       </c>
       <c r="O3">
-        <v>0.9907039738972513</v>
+        <v>0.9791468442752934</v>
       </c>
       <c r="P3">
-        <v>3218.5</v>
+        <v>1234.9</v>
       </c>
       <c r="Q3">
-        <v>0.09290584424956556</v>
+        <v>0.03880136491318473</v>
       </c>
       <c r="R3">
-        <v>0.9907039738972513</v>
+        <v>0.9791468442752934</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>54131.4</v>
+        <v>6512.7</v>
       </c>
       <c r="V3">
-        <v>1.562567474727648</v>
+        <v>0.2046332895538895</v>
       </c>
       <c r="W3">
-        <v>0.08186649665221039</v>
+        <v>0.05332296075189941</v>
       </c>
       <c r="X3">
-        <v>0.04552847491886295</v>
+        <v>0.07538161512773187</v>
       </c>
       <c r="Y3">
-        <v>0.03633802173334744</v>
+        <v>-0.02205865437583245</v>
       </c>
       <c r="Z3">
-        <v>0.3116895494835689</v>
+        <v>0.1238893022215883</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04279980004630634</v>
+        <v>0.07021293798687403</v>
       </c>
       <c r="AC3">
-        <v>-0.04279980004630634</v>
+        <v>-0.07021293798687403</v>
       </c>
       <c r="AD3">
-        <v>4972.2</v>
+        <v>7150</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4972.2</v>
+        <v>7150</v>
       </c>
       <c r="AG3">
-        <v>-49159.2</v>
+        <v>637.3000000000002</v>
       </c>
       <c r="AH3">
-        <v>0.1255136969011582</v>
+        <v>0.1834452819926006</v>
       </c>
       <c r="AI3">
-        <v>0.1069893144094092</v>
+        <v>0.2350813743218806</v>
       </c>
       <c r="AJ3">
-        <v>3.386412796384827</v>
+        <v>0.01963127820475304</v>
       </c>
       <c r="AK3">
-        <v>6.419661512745503</v>
+        <v>0.02666270609941303</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hang Seng Bank Limited (SEHK:11)</t>
+          <t>Dah Sing Banking Group Limited (SEHK:2356)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +838,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.05230000000000001</v>
+        <v>-0.0202</v>
       </c>
       <c r="E4">
-        <v>0.0109</v>
-      </c>
-      <c r="F4">
-        <v>0.08439999999999999</v>
+        <v>-0.0704</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,28 +856,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2100.4</v>
+        <v>209.8</v>
       </c>
       <c r="L4">
-        <v>0.4975482648347744</v>
+        <v>0.4001525843982454</v>
       </c>
       <c r="M4">
-        <v>1444.2</v>
+        <v>66.2</v>
       </c>
       <c r="N4">
-        <v>0.04127818904164404</v>
+        <v>0.06557052297939778</v>
       </c>
       <c r="O4">
-        <v>0.6875833174633403</v>
+        <v>0.3155386081982841</v>
       </c>
       <c r="P4">
-        <v>1444.2</v>
+        <v>66.2</v>
       </c>
       <c r="Q4">
-        <v>0.04127818904164404</v>
+        <v>0.06557052297939778</v>
       </c>
       <c r="R4">
-        <v>0.6875833174633403</v>
+        <v>0.3155386081982841</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -889,55 +886,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5405</v>
+        <v>2512.4</v>
       </c>
       <c r="V4">
-        <v>0.1544859519250007</v>
+        <v>2.48851030110935</v>
       </c>
       <c r="W4">
-        <v>0.09248463286189831</v>
+        <v>0.05420068202955462</v>
       </c>
       <c r="X4">
-        <v>0.04728883857333798</v>
+        <v>0.08875877466822962</v>
       </c>
       <c r="Y4">
-        <v>0.04519579428856033</v>
+        <v>-0.03455809263867501</v>
       </c>
       <c r="Z4">
-        <v>0.276846902974063</v>
+        <v>0.2115307028161059</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04314743425748965</v>
+        <v>0.07034469922533894</v>
       </c>
       <c r="AC4">
-        <v>-0.04314743425748965</v>
+        <v>-0.07034469922533894</v>
       </c>
       <c r="AD4">
-        <v>7736.2</v>
+        <v>751.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>7736.2</v>
+        <v>751.9</v>
       </c>
       <c r="AG4">
-        <v>2331.2</v>
+        <v>-1760.5</v>
       </c>
       <c r="AH4">
-        <v>0.1810772601303273</v>
+        <v>0.4268521146749929</v>
       </c>
       <c r="AI4">
-        <v>0.2463765808171363</v>
+        <v>0.1617128355127323</v>
       </c>
       <c r="AJ4">
-        <v>0.0624681790654426</v>
+        <v>2.344519909442003</v>
       </c>
       <c r="AK4">
-        <v>0.08967912936768364</v>
+        <v>-0.8237413438143366</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dah Sing Banking Group Limited (SEHK:2356)</t>
+          <t>Dah Sing Financial Holdings Limited (SEHK:440)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,10 +960,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0216</v>
+        <v>-0.0145</v>
       </c>
       <c r="E5">
-        <v>-0.0395</v>
+        <v>-0.264</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,28 +978,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>213.4</v>
+        <v>160.6</v>
       </c>
       <c r="L5">
-        <v>0.3792429358450329</v>
+        <v>0.287298747763864</v>
       </c>
       <c r="M5">
-        <v>59.6</v>
+        <v>43.2</v>
       </c>
       <c r="N5">
-        <v>0.04964184574379477</v>
+        <v>0.05829959514170041</v>
       </c>
       <c r="O5">
-        <v>0.2792877225866917</v>
+        <v>0.2689912826899128</v>
       </c>
       <c r="P5">
-        <v>59.6</v>
+        <v>43.2</v>
       </c>
       <c r="Q5">
-        <v>0.04964184574379477</v>
+        <v>0.05829959514170041</v>
       </c>
       <c r="R5">
-        <v>0.2792877225866917</v>
+        <v>0.2689912826899128</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1011,55 +1008,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2113.3</v>
+        <v>3178.1</v>
       </c>
       <c r="V5">
-        <v>1.760203231717475</v>
+        <v>4.2889338731444</v>
       </c>
       <c r="W5">
-        <v>0.0590252807434862</v>
+        <v>0.04234003849094408</v>
       </c>
       <c r="X5">
-        <v>0.05763587432871833</v>
+        <v>0.09575092149142753</v>
       </c>
       <c r="Y5">
-        <v>0.001389406414767869</v>
+        <v>-0.05341088300048345</v>
       </c>
       <c r="Z5">
-        <v>0.5001777777777779</v>
+        <v>0.1483900082291418</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04396981268683946</v>
+        <v>0.07047890581229227</v>
       </c>
       <c r="AC5">
-        <v>-0.04396981268683946</v>
+        <v>-0.07047890581229227</v>
       </c>
       <c r="AD5">
-        <v>813</v>
+        <v>753.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>813</v>
+        <v>753.3</v>
       </c>
       <c r="AG5">
-        <v>-1300.3</v>
+        <v>-2424.8</v>
       </c>
       <c r="AH5">
-        <v>0.4037544696066746</v>
+        <v>0.5041156394298334</v>
       </c>
       <c r="AI5">
-        <v>0.173577010119988</v>
+        <v>0.1379468209786112</v>
       </c>
       <c r="AJ5">
-        <v>13.04212637913738</v>
+        <v>1.440076018529516</v>
       </c>
       <c r="AK5">
-        <v>-0.5058548920443494</v>
+        <v>-1.062250843299602</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1076,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dah Sing Financial Holdings Limited (SEHK:440)</t>
+          <t>The Bank of East Asia, Limited (SEHK:23)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1085,10 +1082,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0423</v>
+        <v>0.0216</v>
       </c>
       <c r="E6">
-        <v>-0.0625</v>
+        <v>-0.122</v>
+      </c>
+      <c r="F6">
+        <v>0.156</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1103,215 +1103,90 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>166.7</v>
+        <v>522.2</v>
       </c>
       <c r="L6">
-        <v>0.2763136084866567</v>
+        <v>0.2921725507749119</v>
       </c>
       <c r="M6">
-        <v>38.7</v>
+        <v>1217.9</v>
       </c>
       <c r="N6">
-        <v>0.04001240694789082</v>
+        <v>0.3746347165400351</v>
       </c>
       <c r="O6">
-        <v>0.2321535692861428</v>
+        <v>2.33224818077365</v>
       </c>
       <c r="P6">
-        <v>38.7</v>
+        <v>346.1</v>
       </c>
       <c r="Q6">
-        <v>0.04001240694789082</v>
+        <v>0.1064628256790427</v>
       </c>
       <c r="R6">
-        <v>0.2321535692861428</v>
+        <v>0.6627728839525086</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>871.8000000000001</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.7158223171032104</v>
       </c>
       <c r="U6">
-        <v>740</v>
+        <v>15492.9</v>
       </c>
       <c r="V6">
-        <v>0.7650951199338296</v>
+        <v>4.765726414223753</v>
       </c>
       <c r="W6">
-        <v>0.04827406463570022</v>
+        <v>0.03550448735382105</v>
       </c>
       <c r="X6">
-        <v>0.06136686531346404</v>
+        <v>0.08974926994247445</v>
       </c>
       <c r="Y6">
-        <v>-0.01309280067776382</v>
+        <v>-0.0542447825886534</v>
       </c>
       <c r="Z6">
-        <v>0.2284189004997728</v>
+        <v>0.3643164353125827</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04419369226177809</v>
+        <v>0.07319022301768496</v>
       </c>
       <c r="AC6">
-        <v>-0.04419369226177809</v>
+        <v>-0.07319022301768496</v>
       </c>
       <c r="AD6">
-        <v>814</v>
+        <v>2546.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>814</v>
+        <v>2546.3</v>
       </c>
       <c r="AG6">
-        <v>74</v>
+        <v>-12946.6</v>
       </c>
       <c r="AH6">
-        <v>0.4569952840781495</v>
+        <v>0.4392292831021872</v>
       </c>
       <c r="AI6">
-        <v>0.1461400359066427</v>
+        <v>0.1582014625387536</v>
       </c>
       <c r="AJ6">
-        <v>0.07107184018440262</v>
+        <v>1.335292964922595</v>
       </c>
       <c r="AK6">
-        <v>0.01532091097308489</v>
+        <v>-21.49169986719782</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>The Bank of East Asia, Limited (SEHK:23)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.0123</v>
-      </c>
-      <c r="E7">
-        <v>0.022</v>
-      </c>
-      <c r="F7">
-        <v>0.215</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>612</v>
-      </c>
-      <c r="L7">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="M7">
-        <v>899.7</v>
-      </c>
-      <c r="N7">
-        <v>0.2143265520034304</v>
-      </c>
-      <c r="O7">
-        <v>1.470098039215686</v>
-      </c>
-      <c r="P7">
-        <v>250.7</v>
-      </c>
-      <c r="Q7">
-        <v>0.05972175901662775</v>
-      </c>
-      <c r="R7">
-        <v>0.409640522875817</v>
-      </c>
-      <c r="S7">
-        <v>649</v>
-      </c>
-      <c r="T7">
-        <v>0.7213515616316549</v>
-      </c>
-      <c r="U7">
-        <v>12985.8</v>
-      </c>
-      <c r="V7">
-        <v>3.093477535852112</v>
-      </c>
-      <c r="W7">
-        <v>0.04447092676830066</v>
-      </c>
-      <c r="X7">
-        <v>0.05947954454237996</v>
-      </c>
-      <c r="Y7">
-        <v>-0.0150086177740793</v>
-      </c>
-      <c r="Z7">
-        <v>0.3155181302629318</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.04574874917076176</v>
-      </c>
-      <c r="AC7">
-        <v>-0.04574874917076176</v>
-      </c>
-      <c r="AD7">
-        <v>3183.7</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>3183.7</v>
-      </c>
-      <c r="AG7">
-        <v>-9802.099999999999</v>
-      </c>
-      <c r="AH7">
-        <v>0.4313079997290523</v>
-      </c>
-      <c r="AI7">
-        <v>0.1775766094396662</v>
-      </c>
-      <c r="AJ7">
-        <v>1.749031993290866</v>
-      </c>
-      <c r="AK7">
-        <v>-1.983106741118394</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.01735</v>
+        <v>5e-05</v>
       </c>
       <c r="E2">
-        <v>-0.1175</v>
+        <v>-0.0504</v>
       </c>
       <c r="F2">
-        <v>0.163</v>
+        <v>0.127</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>2153.8</v>
+        <v>7105</v>
       </c>
       <c r="L2">
-        <v>0.3539872460719217</v>
+        <v>0.4675787908103164</v>
       </c>
       <c r="M2">
-        <v>2562.2</v>
+        <v>3350.46</v>
       </c>
       <c r="N2">
-        <v>0.06957263147033348</v>
+        <v>0.06003666213317708</v>
       </c>
       <c r="O2">
-        <v>1.189618348964621</v>
+        <v>0.4715636875439831</v>
       </c>
       <c r="P2">
-        <v>1690.4</v>
+        <v>3193.1</v>
       </c>
       <c r="Q2">
-        <v>0.04590023270527347</v>
+        <v>0.05721693912401513</v>
       </c>
       <c r="R2">
-        <v>0.7848453895440617</v>
+        <v>0.4494159042927516</v>
       </c>
       <c r="S2">
-        <v>871.8000000000001</v>
+        <v>157.36</v>
       </c>
       <c r="T2">
-        <v>0.3402544688158614</v>
+        <v>0.04696668517158836</v>
       </c>
       <c r="U2">
-        <v>27696.1</v>
+        <v>69189.10000000001</v>
       </c>
       <c r="V2">
-        <v>0.7520453354404428</v>
+        <v>1.239794720724498</v>
       </c>
       <c r="W2">
-        <v>0.04783149962142175</v>
+        <v>0.05308258716679067</v>
       </c>
       <c r="X2">
-        <v>0.08925402230535204</v>
+        <v>0.07472535224907698</v>
       </c>
       <c r="Y2">
-        <v>-0.04142252268393029</v>
+        <v>-0.0216427650822863</v>
       </c>
       <c r="Z2">
-        <v>0.1640331603423873</v>
+        <v>0.407000974961698</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0704118025188156</v>
+        <v>0.06072919028913304</v>
       </c>
       <c r="AC2">
-        <v>-0.0704118025188156</v>
+        <v>-0.06072919028913304</v>
       </c>
       <c r="AD2">
-        <v>11201.5</v>
+        <v>29363.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11201.5</v>
+        <v>29363.1</v>
       </c>
       <c r="AG2">
-        <v>-16494.6</v>
+        <v>-39826.00000000001</v>
       </c>
       <c r="AH2">
-        <v>0.2332227061870695</v>
+        <v>0.3447587178584008</v>
       </c>
       <c r="AI2">
-        <v>0.1978340077038963</v>
+        <v>0.2543442275759379</v>
       </c>
       <c r="AJ2">
-        <v>-0.8112191451377307</v>
+        <v>-2.492099944308519</v>
       </c>
       <c r="AK2">
-        <v>-0.5702619915227868</v>
+        <v>-0.8609686708231371</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hang Seng Bank Limited (SEHK:11)</t>
+          <t>BOC Hong Kong (Holdings) Limited (SEHK:2388)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0355</v>
+        <v>0.0321</v>
       </c>
       <c r="E3">
-        <v>-0.113</v>
+        <v>0.009950000000000001</v>
       </c>
       <c r="F3">
-        <v>0.17</v>
+        <v>0.095</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1261.2</v>
+        <v>4188.5</v>
       </c>
       <c r="L3">
-        <v>0.3924326342647333</v>
+        <v>0.5415836975354935</v>
       </c>
       <c r="M3">
-        <v>1234.9</v>
+        <v>1702.3</v>
       </c>
       <c r="N3">
-        <v>0.03880136491318473</v>
+        <v>0.05932847264819049</v>
       </c>
       <c r="O3">
-        <v>0.9791468442752934</v>
+        <v>0.4064223469022323</v>
       </c>
       <c r="P3">
-        <v>1234.9</v>
+        <v>1702.3</v>
       </c>
       <c r="Q3">
-        <v>0.03880136491318473</v>
+        <v>0.05932847264819049</v>
       </c>
       <c r="R3">
-        <v>0.9791468442752934</v>
+        <v>0.4064223469022323</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6512.7</v>
+        <v>37635.8</v>
       </c>
       <c r="V3">
-        <v>0.2046332895538895</v>
+        <v>1.311680979200357</v>
       </c>
       <c r="W3">
-        <v>0.05332296075189941</v>
+        <v>0.1029672058606618</v>
       </c>
       <c r="X3">
-        <v>0.07538161512773187</v>
+        <v>0.07132005589765834</v>
       </c>
       <c r="Y3">
-        <v>-0.02205865437583245</v>
+        <v>0.03164714996300344</v>
       </c>
       <c r="Z3">
-        <v>0.1238893022215883</v>
+        <v>0.8012556852912839</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07021293798687403</v>
+        <v>0.060625634878174</v>
       </c>
       <c r="AC3">
-        <v>-0.07021293798687403</v>
+        <v>-0.060625634878174</v>
       </c>
       <c r="AD3">
-        <v>7150</v>
+        <v>17472.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7150</v>
+        <v>17472.6</v>
       </c>
       <c r="AG3">
-        <v>637.3000000000002</v>
+        <v>-20163.2</v>
       </c>
       <c r="AH3">
-        <v>0.1834452819926006</v>
+        <v>0.3784782542770126</v>
       </c>
       <c r="AI3">
-        <v>0.2350813743218806</v>
+        <v>0.2904374364191251</v>
       </c>
       <c r="AJ3">
-        <v>0.01963127820475304</v>
+        <v>-2.363909210279499</v>
       </c>
       <c r="AK3">
-        <v>0.02666270609941303</v>
+        <v>-0.8951953045223279</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0202</v>
+        <v>0.0005600000000000001</v>
       </c>
       <c r="E4">
-        <v>-0.0704</v>
+        <v>-0.0621</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,85 +856,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>209.8</v>
+        <v>206.9</v>
       </c>
       <c r="L4">
-        <v>0.4001525843982454</v>
+        <v>0.3638122032706172</v>
       </c>
       <c r="M4">
-        <v>66.2</v>
+        <v>189.2</v>
       </c>
       <c r="N4">
-        <v>0.06557052297939778</v>
+        <v>0.2085997794928335</v>
       </c>
       <c r="O4">
-        <v>0.3155386081982841</v>
+        <v>0.9144514258095697</v>
       </c>
       <c r="P4">
-        <v>66.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="Q4">
-        <v>0.06557052297939778</v>
+        <v>0.08257993384785006</v>
       </c>
       <c r="R4">
-        <v>0.3155386081982841</v>
+        <v>0.3620106331561141</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>114.3</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.6041226215644819</v>
       </c>
       <c r="U4">
-        <v>2512.4</v>
+        <v>2478.9</v>
       </c>
       <c r="V4">
-        <v>2.48851030110935</v>
+        <v>2.733076074972437</v>
       </c>
       <c r="W4">
-        <v>0.05420068202955462</v>
+        <v>0.05308258716679067</v>
       </c>
       <c r="X4">
-        <v>0.08875877466822962</v>
+        <v>0.07472535224907698</v>
       </c>
       <c r="Y4">
-        <v>-0.03455809263867501</v>
+        <v>-0.0216427650822863</v>
       </c>
       <c r="Z4">
-        <v>0.2115307028161059</v>
+        <v>0.2779162390656308</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07034469922533894</v>
+        <v>0.06067183628797447</v>
       </c>
       <c r="AC4">
-        <v>-0.07034469922533894</v>
+        <v>-0.06067183628797447</v>
       </c>
       <c r="AD4">
-        <v>751.9</v>
+        <v>723.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>751.9</v>
+        <v>723.9</v>
       </c>
       <c r="AG4">
-        <v>-1760.5</v>
+        <v>-1755</v>
       </c>
       <c r="AH4">
-        <v>0.4268521146749929</v>
+        <v>0.4438653504200135</v>
       </c>
       <c r="AI4">
-        <v>0.1617128355127323</v>
+        <v>0.1552101200686106</v>
       </c>
       <c r="AJ4">
-        <v>2.344519909442003</v>
+        <v>2.069575471698113</v>
       </c>
       <c r="AK4">
-        <v>-0.8237413438143366</v>
+        <v>-0.8031669031165622</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0145</v>
+        <v>5e-05</v>
       </c>
       <c r="E5">
-        <v>-0.264</v>
+        <v>-0.0482</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,85 +978,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>160.6</v>
+        <v>159.6</v>
       </c>
       <c r="L5">
-        <v>0.287298747763864</v>
+        <v>0.2691399662731871</v>
       </c>
       <c r="M5">
-        <v>43.2</v>
+        <v>48.76</v>
       </c>
       <c r="N5">
-        <v>0.05829959514170041</v>
+        <v>0.0744996180290298</v>
       </c>
       <c r="O5">
-        <v>0.2689912826899128</v>
+        <v>0.3055137844611529</v>
       </c>
       <c r="P5">
-        <v>43.2</v>
+        <v>46.4</v>
       </c>
       <c r="Q5">
-        <v>0.05829959514170041</v>
+        <v>0.07089381207028266</v>
       </c>
       <c r="R5">
-        <v>0.2689912826899128</v>
+        <v>0.2907268170426065</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.359999999999999</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.04840032813781787</v>
       </c>
       <c r="U5">
-        <v>3178.1</v>
+        <v>2585.5</v>
       </c>
       <c r="V5">
-        <v>4.2889338731444</v>
+        <v>3.950343773873186</v>
       </c>
       <c r="W5">
-        <v>0.04234003849094408</v>
+        <v>0.04265098877605558</v>
       </c>
       <c r="X5">
-        <v>0.09575092149142753</v>
+        <v>0.08025706093390741</v>
       </c>
       <c r="Y5">
-        <v>-0.05341088300048345</v>
+        <v>-0.03760607215785183</v>
       </c>
       <c r="Z5">
-        <v>0.1483900082291418</v>
+        <v>0.4872237285350421</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07047890581229227</v>
+        <v>0.06072919028913304</v>
       </c>
       <c r="AC5">
-        <v>-0.07047890581229227</v>
+        <v>-0.06072919028913304</v>
       </c>
       <c r="AD5">
-        <v>753.3</v>
+        <v>723.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>753.3</v>
+        <v>723.5</v>
       </c>
       <c r="AG5">
-        <v>-2424.8</v>
+        <v>-1862</v>
       </c>
       <c r="AH5">
-        <v>0.5041156394298334</v>
+        <v>0.5250362844702468</v>
       </c>
       <c r="AI5">
-        <v>0.1379468209786112</v>
+        <v>0.1289454454722059</v>
       </c>
       <c r="AJ5">
-        <v>1.440076018529516</v>
+        <v>1.542028985507246</v>
       </c>
       <c r="AK5">
-        <v>-1.062250843299602</v>
+        <v>-0.6154558074965295</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,120 +1073,245 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Hang Seng Bank Limited (SEHK:11)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>-0.0117</v>
+      </c>
+      <c r="E6">
+        <v>-0.08689999999999999</v>
+      </c>
+      <c r="F6">
+        <v>0.151</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1848.7</v>
+      </c>
+      <c r="L6">
+        <v>0.4244615879138541</v>
+      </c>
+      <c r="M6">
+        <v>1188.3</v>
+      </c>
+      <c r="N6">
+        <v>0.05332693093033797</v>
+      </c>
+      <c r="O6">
+        <v>0.6427760047601017</v>
+      </c>
+      <c r="P6">
+        <v>1188.3</v>
+      </c>
+      <c r="Q6">
+        <v>0.05332693093033797</v>
+      </c>
+      <c r="R6">
+        <v>0.6427760047601017</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>13872.8</v>
+      </c>
+      <c r="V6">
+        <v>0.6225648804261488</v>
+      </c>
+      <c r="W6">
+        <v>0.07949517318483799</v>
+      </c>
+      <c r="X6">
+        <v>0.06643445874291497</v>
+      </c>
+      <c r="Y6">
+        <v>0.01306071444192303</v>
+      </c>
+      <c r="Z6">
+        <v>0.1826094612781907</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.06085092421911448</v>
+      </c>
+      <c r="AC6">
+        <v>-0.06085092421911448</v>
+      </c>
+      <c r="AD6">
+        <v>7521.7</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>7521.7</v>
+      </c>
+      <c r="AG6">
+        <v>-6351.099999999999</v>
+      </c>
+      <c r="AH6">
+        <v>0.2523636973662137</v>
+      </c>
+      <c r="AI6">
+        <v>0.2648905636456481</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.3986329571559483</v>
+      </c>
+      <c r="AK6">
+        <v>-0.4373222610120707</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>The Bank of East Asia, Limited (SEHK:23)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.0216</v>
-      </c>
-      <c r="E6">
-        <v>-0.122</v>
-      </c>
-      <c r="F6">
-        <v>0.156</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>522.2</v>
-      </c>
-      <c r="L6">
-        <v>0.2921725507749119</v>
-      </c>
-      <c r="M6">
-        <v>1217.9</v>
-      </c>
-      <c r="N6">
-        <v>0.3746347165400351</v>
-      </c>
-      <c r="O6">
-        <v>2.33224818077365</v>
-      </c>
-      <c r="P6">
-        <v>346.1</v>
-      </c>
-      <c r="Q6">
-        <v>0.1064628256790427</v>
-      </c>
-      <c r="R6">
-        <v>0.6627728839525086</v>
-      </c>
-      <c r="S6">
-        <v>871.8000000000001</v>
-      </c>
-      <c r="T6">
-        <v>0.7158223171032104</v>
-      </c>
-      <c r="U6">
-        <v>15492.9</v>
-      </c>
-      <c r="V6">
-        <v>4.765726414223753</v>
-      </c>
-      <c r="W6">
-        <v>0.03550448735382105</v>
-      </c>
-      <c r="X6">
-        <v>0.08974926994247445</v>
-      </c>
-      <c r="Y6">
-        <v>-0.0542447825886534</v>
-      </c>
-      <c r="Z6">
-        <v>0.3643164353125827</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.07319022301768496</v>
-      </c>
-      <c r="AC6">
-        <v>-0.07319022301768496</v>
-      </c>
-      <c r="AD6">
-        <v>2546.3</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>2546.3</v>
-      </c>
-      <c r="AG6">
-        <v>-12946.6</v>
-      </c>
-      <c r="AH6">
-        <v>0.4392292831021872</v>
-      </c>
-      <c r="AI6">
-        <v>0.1582014625387536</v>
-      </c>
-      <c r="AJ6">
-        <v>1.335292964922595</v>
-      </c>
-      <c r="AK6">
-        <v>-21.49169986719782</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
+      <c r="D7">
+        <v>-0.0183</v>
+      </c>
+      <c r="E7">
+        <v>-0.0504</v>
+      </c>
+      <c r="F7">
+        <v>0.127</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>701.3</v>
+      </c>
+      <c r="L7">
+        <v>0.3606768154700679</v>
+      </c>
+      <c r="M7">
+        <v>221.9</v>
+      </c>
+      <c r="N7">
+        <v>0.06787385678891504</v>
+      </c>
+      <c r="O7">
+        <v>0.3164123770141166</v>
+      </c>
+      <c r="P7">
+        <v>181.2</v>
+      </c>
+      <c r="Q7">
+        <v>0.05542470865322852</v>
+      </c>
+      <c r="R7">
+        <v>0.2583772993012976</v>
+      </c>
+      <c r="S7">
+        <v>40.69999999999999</v>
+      </c>
+      <c r="T7">
+        <v>0.1834159531320414</v>
+      </c>
+      <c r="U7">
+        <v>12616.1</v>
+      </c>
+      <c r="V7">
+        <v>3.858960633774814</v>
+      </c>
+      <c r="W7">
+        <v>0.05189049204587495</v>
+      </c>
+      <c r="X7">
+        <v>0.07644373934135885</v>
+      </c>
+      <c r="Y7">
+        <v>-0.0245532472954839</v>
+      </c>
+      <c r="Z7">
+        <v>3.42083040112597</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.06298179301861187</v>
+      </c>
+      <c r="AC7">
+        <v>-0.06298179301861187</v>
+      </c>
+      <c r="AD7">
+        <v>2921.4</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>2921.4</v>
+      </c>
+      <c r="AG7">
+        <v>-9694.700000000001</v>
+      </c>
+      <c r="AH7">
+        <v>0.4719014004878285</v>
+      </c>
+      <c r="AI7">
+        <v>0.175815313878541</v>
+      </c>
+      <c r="AJ7">
+        <v>1.508808790114234</v>
+      </c>
+      <c r="AK7">
+        <v>-2.423553822308885</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>5e-05</v>
+        <v>0.00395</v>
       </c>
       <c r="E2">
-        <v>-0.0504</v>
+        <v>-0.030905</v>
       </c>
       <c r="F2">
-        <v>0.127</v>
+        <v>0.02855</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>7105</v>
+        <v>2754.4</v>
       </c>
       <c r="L2">
-        <v>0.4675787908103164</v>
+        <v>0.4321847737400363</v>
       </c>
       <c r="M2">
-        <v>3350.46</v>
+        <v>2252.7</v>
       </c>
       <c r="N2">
-        <v>0.06003666213317708</v>
+        <v>0.08503000792662212</v>
       </c>
       <c r="O2">
-        <v>0.4715636875439831</v>
+        <v>0.8178550682544293</v>
       </c>
       <c r="P2">
-        <v>3193.1</v>
+        <v>1958.9</v>
       </c>
       <c r="Q2">
-        <v>0.05721693912401513</v>
+        <v>0.07394028611331295</v>
       </c>
       <c r="R2">
-        <v>0.4494159042927516</v>
+        <v>0.7111893697356957</v>
       </c>
       <c r="S2">
-        <v>157.36</v>
+        <v>293.8000000000001</v>
       </c>
       <c r="T2">
-        <v>0.04696668517158836</v>
+        <v>0.1304212722510765</v>
       </c>
       <c r="U2">
-        <v>69189.10000000001</v>
+        <v>21289.3</v>
       </c>
       <c r="V2">
-        <v>1.239794720724498</v>
+        <v>0.80358207828483</v>
       </c>
       <c r="W2">
-        <v>0.05308258716679067</v>
+        <v>0.07181389321675893</v>
       </c>
       <c r="X2">
-        <v>0.07472535224907698</v>
+        <v>0.07778865701817481</v>
       </c>
       <c r="Y2">
-        <v>-0.0216427650822863</v>
+        <v>-0.005974763801415872</v>
       </c>
       <c r="Z2">
-        <v>0.407000974961698</v>
+        <v>0.3455788657473933</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06072919028913304</v>
+        <v>0.06650507456965782</v>
       </c>
       <c r="AC2">
-        <v>-0.06072919028913304</v>
+        <v>-0.06650507456965782</v>
       </c>
       <c r="AD2">
-        <v>29363.1</v>
+        <v>11529.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>29363.1</v>
+        <v>11529.7</v>
       </c>
       <c r="AG2">
-        <v>-39826.00000000001</v>
+        <v>-9759.599999999999</v>
       </c>
       <c r="AH2">
-        <v>0.3447587178584008</v>
+        <v>0.3032320166637298</v>
       </c>
       <c r="AI2">
-        <v>0.2543442275759379</v>
+        <v>0.2461265546082152</v>
       </c>
       <c r="AJ2">
-        <v>-2.492099944308519</v>
+        <v>-0.5832407042203017</v>
       </c>
       <c r="AK2">
-        <v>-0.8609686708231371</v>
+        <v>-0.3819012103164509</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BOC Hong Kong (Holdings) Limited (SEHK:2388)</t>
+          <t>Hang Seng Bank Limited (SEHK:11)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0321</v>
+        <v>-0.0188</v>
       </c>
       <c r="E3">
-        <v>0.009950000000000001</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="F3">
-        <v>0.095</v>
+        <v>-0.0148</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>4188.5</v>
+        <v>2294.2</v>
       </c>
       <c r="L3">
-        <v>0.5415836975354935</v>
+        <v>0.5047633715429802</v>
       </c>
       <c r="M3">
-        <v>1702.3</v>
+        <v>1955</v>
       </c>
       <c r="N3">
-        <v>0.05932847264819049</v>
+        <v>0.08443356093684543</v>
       </c>
       <c r="O3">
-        <v>0.4064223469022323</v>
+        <v>0.8521488972190743</v>
       </c>
       <c r="P3">
-        <v>1702.3</v>
+        <v>1705.1</v>
       </c>
       <c r="Q3">
-        <v>0.05932847264819049</v>
+        <v>0.07364074923448344</v>
       </c>
       <c r="R3">
-        <v>0.4064223469022323</v>
+        <v>0.7432220381832447</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>249.9000000000001</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.1278260869565218</v>
       </c>
       <c r="U3">
-        <v>37635.8</v>
+        <v>10561.8</v>
       </c>
       <c r="V3">
-        <v>1.311680979200357</v>
+        <v>0.4561485339656133</v>
       </c>
       <c r="W3">
-        <v>0.1029672058606618</v>
+        <v>0.1099465650684111</v>
       </c>
       <c r="X3">
-        <v>0.07132005589765834</v>
+        <v>0.07184967881340795</v>
       </c>
       <c r="Y3">
-        <v>0.03164714996300344</v>
+        <v>0.03809688625500313</v>
       </c>
       <c r="Z3">
-        <v>0.8012556852912839</v>
+        <v>0.3140312573410532</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.060625634878174</v>
+        <v>0.06598164400946813</v>
       </c>
       <c r="AC3">
-        <v>-0.060625634878174</v>
+        <v>-0.06598164400946813</v>
       </c>
       <c r="AD3">
-        <v>17472.6</v>
+        <v>8022.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>17472.6</v>
+        <v>8022.3</v>
       </c>
       <c r="AG3">
-        <v>-20163.2</v>
+        <v>-2539.499999999999</v>
       </c>
       <c r="AH3">
-        <v>0.3784782542770126</v>
+        <v>0.2573179884913686</v>
       </c>
       <c r="AI3">
-        <v>0.2904374364191251</v>
+        <v>0.2735297727830665</v>
       </c>
       <c r="AJ3">
-        <v>-2.363909210279499</v>
+        <v>-0.1231881948891088</v>
       </c>
       <c r="AK3">
-        <v>-0.8951953045223279</v>
+        <v>-0.1353173123035114</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dah Sing Banking Group Limited (SEHK:2356)</t>
+          <t>The Bank of East Asia, Limited (SEHK:23)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,10 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0005600000000000001</v>
+        <v>0.0267</v>
       </c>
       <c r="E4">
-        <v>-0.0621</v>
+        <v>0.00429</v>
+      </c>
+      <c r="F4">
+        <v>0.07190000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,462 +859,90 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>206.9</v>
+        <v>460.2</v>
       </c>
       <c r="L4">
-        <v>0.3638122032706172</v>
+        <v>0.2517367758875335</v>
       </c>
       <c r="M4">
-        <v>189.2</v>
+        <v>297.7</v>
       </c>
       <c r="N4">
-        <v>0.2085997794928335</v>
+        <v>0.08916644202833439</v>
       </c>
       <c r="O4">
-        <v>0.9144514258095697</v>
+        <v>0.6468926553672316</v>
       </c>
       <c r="P4">
-        <v>74.90000000000001</v>
+        <v>253.8</v>
       </c>
       <c r="Q4">
-        <v>0.08257993384785006</v>
+        <v>0.07601761164525116</v>
       </c>
       <c r="R4">
-        <v>0.3620106331561141</v>
+        <v>0.5514993481095176</v>
       </c>
       <c r="S4">
-        <v>114.3</v>
+        <v>43.89999999999998</v>
       </c>
       <c r="T4">
-        <v>0.6041226215644819</v>
+        <v>0.1474638898219683</v>
       </c>
       <c r="U4">
-        <v>2478.9</v>
+        <v>10727.5</v>
       </c>
       <c r="V4">
-        <v>2.733076074972437</v>
+        <v>3.213076946116752</v>
       </c>
       <c r="W4">
-        <v>0.05308258716679067</v>
+        <v>0.03368122136510678</v>
       </c>
       <c r="X4">
-        <v>0.07472535224907698</v>
+        <v>0.08372763522294165</v>
       </c>
       <c r="Y4">
-        <v>-0.0216427650822863</v>
+        <v>-0.05004641385783486</v>
       </c>
       <c r="Z4">
-        <v>0.2779162390656308</v>
+        <v>0.4606294252526017</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06067183628797447</v>
+        <v>0.0670285051298475</v>
       </c>
       <c r="AC4">
-        <v>-0.06067183628797447</v>
+        <v>-0.0670285051298475</v>
       </c>
       <c r="AD4">
-        <v>723.9</v>
+        <v>3507.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>723.9</v>
+        <v>3507.4</v>
       </c>
       <c r="AG4">
-        <v>-1755</v>
+        <v>-7220.1</v>
       </c>
       <c r="AH4">
-        <v>0.4438653504200135</v>
+        <v>0.5123208834226786</v>
       </c>
       <c r="AI4">
-        <v>0.1552101200686106</v>
+        <v>0.2002420671622193</v>
       </c>
       <c r="AJ4">
-        <v>2.069575471698113</v>
+        <v>1.860179316741382</v>
       </c>
       <c r="AK4">
-        <v>-0.8031669031165622</v>
+        <v>-1.063609445663863</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Dah Sing Financial Holdings Limited (SEHK:440)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>5e-05</v>
-      </c>
-      <c r="E5">
-        <v>-0.0482</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>159.6</v>
-      </c>
-      <c r="L5">
-        <v>0.2691399662731871</v>
-      </c>
-      <c r="M5">
-        <v>48.76</v>
-      </c>
-      <c r="N5">
-        <v>0.0744996180290298</v>
-      </c>
-      <c r="O5">
-        <v>0.3055137844611529</v>
-      </c>
-      <c r="P5">
-        <v>46.4</v>
-      </c>
-      <c r="Q5">
-        <v>0.07089381207028266</v>
-      </c>
-      <c r="R5">
-        <v>0.2907268170426065</v>
-      </c>
-      <c r="S5">
-        <v>2.359999999999999</v>
-      </c>
-      <c r="T5">
-        <v>0.04840032813781787</v>
-      </c>
-      <c r="U5">
-        <v>2585.5</v>
-      </c>
-      <c r="V5">
-        <v>3.950343773873186</v>
-      </c>
-      <c r="W5">
-        <v>0.04265098877605558</v>
-      </c>
-      <c r="X5">
-        <v>0.08025706093390741</v>
-      </c>
-      <c r="Y5">
-        <v>-0.03760607215785183</v>
-      </c>
-      <c r="Z5">
-        <v>0.4872237285350421</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.06072919028913304</v>
-      </c>
-      <c r="AC5">
-        <v>-0.06072919028913304</v>
-      </c>
-      <c r="AD5">
-        <v>723.5</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>723.5</v>
-      </c>
-      <c r="AG5">
-        <v>-1862</v>
-      </c>
-      <c r="AH5">
-        <v>0.5250362844702468</v>
-      </c>
-      <c r="AI5">
-        <v>0.1289454454722059</v>
-      </c>
-      <c r="AJ5">
-        <v>1.542028985507246</v>
-      </c>
-      <c r="AK5">
-        <v>-0.6154558074965295</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Hang Seng Bank Limited (SEHK:11)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>-0.0117</v>
-      </c>
-      <c r="E6">
-        <v>-0.08689999999999999</v>
-      </c>
-      <c r="F6">
-        <v>0.151</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>1848.7</v>
-      </c>
-      <c r="L6">
-        <v>0.4244615879138541</v>
-      </c>
-      <c r="M6">
-        <v>1188.3</v>
-      </c>
-      <c r="N6">
-        <v>0.05332693093033797</v>
-      </c>
-      <c r="O6">
-        <v>0.6427760047601017</v>
-      </c>
-      <c r="P6">
-        <v>1188.3</v>
-      </c>
-      <c r="Q6">
-        <v>0.05332693093033797</v>
-      </c>
-      <c r="R6">
-        <v>0.6427760047601017</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>13872.8</v>
-      </c>
-      <c r="V6">
-        <v>0.6225648804261488</v>
-      </c>
-      <c r="W6">
-        <v>0.07949517318483799</v>
-      </c>
-      <c r="X6">
-        <v>0.06643445874291497</v>
-      </c>
-      <c r="Y6">
-        <v>0.01306071444192303</v>
-      </c>
-      <c r="Z6">
-        <v>0.1826094612781907</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.06085092421911448</v>
-      </c>
-      <c r="AC6">
-        <v>-0.06085092421911448</v>
-      </c>
-      <c r="AD6">
-        <v>7521.7</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>7521.7</v>
-      </c>
-      <c r="AG6">
-        <v>-6351.099999999999</v>
-      </c>
-      <c r="AH6">
-        <v>0.2523636973662137</v>
-      </c>
-      <c r="AI6">
-        <v>0.2648905636456481</v>
-      </c>
-      <c r="AJ6">
-        <v>-0.3986329571559483</v>
-      </c>
-      <c r="AK6">
-        <v>-0.4373222610120707</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>The Bank of East Asia, Limited (SEHK:23)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>-0.0183</v>
-      </c>
-      <c r="E7">
-        <v>-0.0504</v>
-      </c>
-      <c r="F7">
-        <v>0.127</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>701.3</v>
-      </c>
-      <c r="L7">
-        <v>0.3606768154700679</v>
-      </c>
-      <c r="M7">
-        <v>221.9</v>
-      </c>
-      <c r="N7">
-        <v>0.06787385678891504</v>
-      </c>
-      <c r="O7">
-        <v>0.3164123770141166</v>
-      </c>
-      <c r="P7">
-        <v>181.2</v>
-      </c>
-      <c r="Q7">
-        <v>0.05542470865322852</v>
-      </c>
-      <c r="R7">
-        <v>0.2583772993012976</v>
-      </c>
-      <c r="S7">
-        <v>40.69999999999999</v>
-      </c>
-      <c r="T7">
-        <v>0.1834159531320414</v>
-      </c>
-      <c r="U7">
-        <v>12616.1</v>
-      </c>
-      <c r="V7">
-        <v>3.858960633774814</v>
-      </c>
-      <c r="W7">
-        <v>0.05189049204587495</v>
-      </c>
-      <c r="X7">
-        <v>0.07644373934135885</v>
-      </c>
-      <c r="Y7">
-        <v>-0.0245532472954839</v>
-      </c>
-      <c r="Z7">
-        <v>3.42083040112597</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.06298179301861187</v>
-      </c>
-      <c r="AC7">
-        <v>-0.06298179301861187</v>
-      </c>
-      <c r="AD7">
-        <v>2921.4</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>2921.4</v>
-      </c>
-      <c r="AG7">
-        <v>-9694.700000000001</v>
-      </c>
-      <c r="AH7">
-        <v>0.4719014004878285</v>
-      </c>
-      <c r="AI7">
-        <v>0.175815313878541</v>
-      </c>
-      <c r="AJ7">
-        <v>1.508808790114234</v>
-      </c>
-      <c r="AK7">
-        <v>-2.423553822308885</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00395</v>
+        <v>0.00655</v>
       </c>
       <c r="E2">
-        <v>-0.030905</v>
+        <v>-0.0216</v>
       </c>
       <c r="F2">
-        <v>0.02855</v>
+        <v>0.0385</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>2754.4</v>
+        <v>7926.8</v>
       </c>
       <c r="L2">
-        <v>0.4321847737400363</v>
+        <v>0.5035062757253925</v>
       </c>
       <c r="M2">
-        <v>2252.7</v>
+        <v>7497.299999999999</v>
       </c>
       <c r="N2">
-        <v>0.08503000792662212</v>
+        <v>0.1188272754504779</v>
       </c>
       <c r="O2">
-        <v>0.8178550682544293</v>
+        <v>0.9458167230155926</v>
       </c>
       <c r="P2">
-        <v>1958.9</v>
+        <v>4188</v>
       </c>
       <c r="Q2">
-        <v>0.07394028611331295</v>
+        <v>0.06637704634823224</v>
       </c>
       <c r="R2">
-        <v>0.7111893697356957</v>
+        <v>0.5283342584649543</v>
       </c>
       <c r="S2">
-        <v>293.8000000000001</v>
+        <v>3309.3</v>
       </c>
       <c r="T2">
-        <v>0.1304212722510765</v>
+        <v>0.4413989036052979</v>
       </c>
       <c r="U2">
-        <v>21289.3</v>
+        <v>115507.5</v>
       </c>
       <c r="V2">
-        <v>0.80358207828483</v>
+        <v>1.830717927666771</v>
       </c>
       <c r="W2">
-        <v>0.07181389321675893</v>
+        <v>0.06969366259739601</v>
       </c>
       <c r="X2">
-        <v>0.07778865701817481</v>
+        <v>0.07498961473887765</v>
       </c>
       <c r="Y2">
-        <v>-0.005974763801415872</v>
+        <v>-0.005295952141481639</v>
       </c>
       <c r="Z2">
-        <v>0.3455788657473933</v>
+        <v>0.3530023767881968</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06650507456965782</v>
+        <v>0.06568992728556858</v>
       </c>
       <c r="AC2">
-        <v>-0.06650507456965782</v>
+        <v>-0.06568992728556858</v>
       </c>
       <c r="AD2">
-        <v>11529.7</v>
+        <v>31112.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11529.7</v>
+        <v>31112.7</v>
       </c>
       <c r="AG2">
-        <v>-9759.599999999999</v>
+        <v>-84394.8</v>
       </c>
       <c r="AH2">
-        <v>0.3032320166637298</v>
+        <v>0.3302595990947575</v>
       </c>
       <c r="AI2">
-        <v>0.2461265546082152</v>
+        <v>0.2627331332535041</v>
       </c>
       <c r="AJ2">
-        <v>-0.5832407042203017</v>
+        <v>3.962066974324787</v>
       </c>
       <c r="AK2">
-        <v>-0.3819012103164509</v>
+        <v>-28.98272605515305</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hang Seng Bank Limited (SEHK:11)</t>
+          <t>Dah Sing Financial Holdings Limited (SEHK:440)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0188</v>
+        <v>0.00655</v>
       </c>
       <c r="E3">
-        <v>-0.06610000000000001</v>
-      </c>
-      <c r="F3">
-        <v>-0.0148</v>
+        <v>-0.0216</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +731,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>2294.2</v>
+        <v>228.3</v>
       </c>
       <c r="L3">
-        <v>0.5047633715429802</v>
+        <v>0.3329444363424238</v>
       </c>
       <c r="M3">
-        <v>1955</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N3">
-        <v>0.08443356093684543</v>
+        <v>0.0705821295735663</v>
       </c>
       <c r="O3">
-        <v>0.8521488972190743</v>
+        <v>0.3574244415243101</v>
       </c>
       <c r="P3">
-        <v>1705.1</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="Q3">
-        <v>0.07364074923448344</v>
+        <v>0.0705821295735663</v>
       </c>
       <c r="R3">
-        <v>0.7432220381832447</v>
+        <v>0.3574244415243101</v>
       </c>
       <c r="S3">
-        <v>249.9000000000001</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.1278260869565218</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>10561.8</v>
+        <v>2333.4</v>
       </c>
       <c r="V3">
-        <v>0.4561485339656133</v>
+        <v>2.018337514055878</v>
       </c>
       <c r="W3">
-        <v>0.1099465650684111</v>
+        <v>0.05866029445771988</v>
       </c>
       <c r="X3">
-        <v>0.07184967881340795</v>
+        <v>0.07670841963303354</v>
       </c>
       <c r="Y3">
-        <v>0.03809688625500313</v>
+        <v>-0.01804812517531366</v>
       </c>
       <c r="Z3">
-        <v>0.3140312573410532</v>
+        <v>0.3553586235489221</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06598164400946813</v>
+        <v>0.06563678406934688</v>
       </c>
       <c r="AC3">
-        <v>-0.06598164400946813</v>
+        <v>-0.06563678406934688</v>
       </c>
       <c r="AD3">
-        <v>8022.3</v>
+        <v>734.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8022.3</v>
+        <v>734.5</v>
       </c>
       <c r="AG3">
-        <v>-2539.499999999999</v>
+        <v>-1598.9</v>
       </c>
       <c r="AH3">
-        <v>0.2573179884913686</v>
+        <v>0.3885010049719666</v>
       </c>
       <c r="AI3">
-        <v>0.2735297727830665</v>
+        <v>0.1191499716116473</v>
       </c>
       <c r="AJ3">
-        <v>-0.1231881948891088</v>
+        <v>3.610885275519421</v>
       </c>
       <c r="AK3">
-        <v>-0.1353173123035114</v>
+        <v>-0.4173474981075931</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,120 +826,492 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>BOC Hong Kong (Holdings) Limited (SEHK:2388)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.029</v>
+      </c>
+      <c r="E4">
+        <v>0.0235</v>
+      </c>
+      <c r="F4">
+        <v>0.0385</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>4669.5</v>
+      </c>
+      <c r="L4">
+        <v>0.5810654421921081</v>
+      </c>
+      <c r="M4">
+        <v>5050.4</v>
+      </c>
+      <c r="N4">
+        <v>0.1487117576043108</v>
+      </c>
+      <c r="O4">
+        <v>1.081571902773316</v>
+      </c>
+      <c r="P4">
+        <v>2034.9</v>
+      </c>
+      <c r="Q4">
+        <v>0.05991873030829481</v>
+      </c>
+      <c r="R4">
+        <v>0.4357854159974301</v>
+      </c>
+      <c r="S4">
+        <v>3015.5</v>
+      </c>
+      <c r="T4">
+        <v>0.5970814192935212</v>
+      </c>
+      <c r="U4">
+        <v>90089.60000000001</v>
+      </c>
+      <c r="V4">
+        <v>2.652736962986956</v>
+      </c>
+      <c r="W4">
+        <v>0.1104020768215929</v>
+      </c>
+      <c r="X4">
+        <v>0.07498961473887765</v>
+      </c>
+      <c r="Y4">
+        <v>0.03541246208271524</v>
+      </c>
+      <c r="Z4">
+        <v>0.3630953994632256</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.06567426554376526</v>
+      </c>
+      <c r="AC4">
+        <v>-0.06567426554376526</v>
+      </c>
+      <c r="AD4">
+        <v>18114.7</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>18114.7</v>
+      </c>
+      <c r="AG4">
+        <v>-71974.90000000001</v>
+      </c>
+      <c r="AH4">
+        <v>0.3478532213681237</v>
+      </c>
+      <c r="AI4">
+        <v>0.3000652650689425</v>
+      </c>
+      <c r="AJ4">
+        <v>1.893383735949218</v>
+      </c>
+      <c r="AK4">
+        <v>2.421733893218126</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dah Sing Banking Group Limited (SEHK:2356)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.005639999999999999</v>
+      </c>
+      <c r="E5">
+        <v>-0.0292</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>274.6</v>
+      </c>
+      <c r="L5">
+        <v>0.4236346806541191</v>
+      </c>
+      <c r="M5">
+        <v>112.6</v>
+      </c>
+      <c r="N5">
+        <v>0.07587601078167115</v>
+      </c>
+      <c r="O5">
+        <v>0.4100509832483612</v>
+      </c>
+      <c r="P5">
+        <v>112.6</v>
+      </c>
+      <c r="Q5">
+        <v>0.07587601078167115</v>
+      </c>
+      <c r="R5">
+        <v>0.4100509832483612</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1795.2</v>
+      </c>
+      <c r="V5">
+        <v>1.209703504043127</v>
+      </c>
+      <c r="W5">
+        <v>0.06969366259739601</v>
+      </c>
+      <c r="X5">
+        <v>0.074333266686399</v>
+      </c>
+      <c r="Y5">
+        <v>-0.004639604089002991</v>
+      </c>
+      <c r="Z5">
+        <v>0.3095363163172724</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.06568992728556858</v>
+      </c>
+      <c r="AC5">
+        <v>-0.06568992728556858</v>
+      </c>
+      <c r="AD5">
+        <v>733.8</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>733.8</v>
+      </c>
+      <c r="AG5">
+        <v>-1061.4</v>
+      </c>
+      <c r="AH5">
+        <v>0.3308684281720624</v>
+      </c>
+      <c r="AI5">
+        <v>0.1455634682906508</v>
+      </c>
+      <c r="AJ5">
+        <v>-2.511594888783721</v>
+      </c>
+      <c r="AK5">
+        <v>-0.3269971348470378</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hang Seng Bank Limited (SEHK:11)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>-0.0188</v>
+      </c>
+      <c r="E6">
+        <v>-0.06610000000000001</v>
+      </c>
+      <c r="F6">
+        <v>-0.0148</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>2294.2</v>
+      </c>
+      <c r="L6">
+        <v>0.5047633715429802</v>
+      </c>
+      <c r="M6">
+        <v>1955</v>
+      </c>
+      <c r="N6">
+        <v>0.08443356093684543</v>
+      </c>
+      <c r="O6">
+        <v>0.8521488972190743</v>
+      </c>
+      <c r="P6">
+        <v>1705.1</v>
+      </c>
+      <c r="Q6">
+        <v>0.07364074923448344</v>
+      </c>
+      <c r="R6">
+        <v>0.7432220381832447</v>
+      </c>
+      <c r="S6">
+        <v>249.9000000000001</v>
+      </c>
+      <c r="T6">
+        <v>0.1278260869565218</v>
+      </c>
+      <c r="U6">
+        <v>10561.8</v>
+      </c>
+      <c r="V6">
+        <v>0.4561485339656133</v>
+      </c>
+      <c r="W6">
+        <v>0.1099465650684111</v>
+      </c>
+      <c r="X6">
+        <v>0.07183751335657977</v>
+      </c>
+      <c r="Y6">
+        <v>0.03810905171183131</v>
+      </c>
+      <c r="Z6">
+        <v>0.3140312573410532</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.06597260894352006</v>
+      </c>
+      <c r="AC6">
+        <v>-0.06597260894352006</v>
+      </c>
+      <c r="AD6">
+        <v>8022.3</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>8022.3</v>
+      </c>
+      <c r="AG6">
+        <v>-2539.499999999999</v>
+      </c>
+      <c r="AH6">
+        <v>0.2573179884913686</v>
+      </c>
+      <c r="AI6">
+        <v>0.2735297727830665</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.1231881948891088</v>
+      </c>
+      <c r="AK6">
+        <v>-0.1353173123035114</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>The Bank of East Asia, Limited (SEHK:23)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D7">
         <v>0.0267</v>
       </c>
-      <c r="E4">
+      <c r="E7">
         <v>0.00429</v>
       </c>
-      <c r="F4">
+      <c r="F7">
         <v>0.07190000000000001</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>460.2</v>
       </c>
-      <c r="L4">
+      <c r="L7">
         <v>0.2517367758875335</v>
       </c>
-      <c r="M4">
+      <c r="M7">
         <v>297.7</v>
       </c>
-      <c r="N4">
+      <c r="N7">
         <v>0.08916644202833439</v>
       </c>
-      <c r="O4">
+      <c r="O7">
         <v>0.6468926553672316</v>
       </c>
-      <c r="P4">
+      <c r="P7">
         <v>253.8</v>
       </c>
-      <c r="Q4">
+      <c r="Q7">
         <v>0.07601761164525116</v>
       </c>
-      <c r="R4">
+      <c r="R7">
         <v>0.5514993481095176</v>
       </c>
-      <c r="S4">
+      <c r="S7">
         <v>43.89999999999998</v>
       </c>
-      <c r="T4">
+      <c r="T7">
         <v>0.1474638898219683</v>
       </c>
-      <c r="U4">
+      <c r="U7">
         <v>10727.5</v>
       </c>
-      <c r="V4">
+      <c r="V7">
         <v>3.213076946116752</v>
       </c>
-      <c r="W4">
+      <c r="W7">
         <v>0.03368122136510678</v>
       </c>
-      <c r="X4">
-        <v>0.08372763522294165</v>
-      </c>
-      <c r="Y4">
-        <v>-0.05004641385783486</v>
-      </c>
-      <c r="Z4">
+      <c r="X7">
+        <v>0.0837099226433661</v>
+      </c>
+      <c r="Y7">
+        <v>-0.05002870127825932</v>
+      </c>
+      <c r="Z7">
         <v>0.4606294252526017</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.0670285051298475</v>
-      </c>
-      <c r="AC4">
-        <v>-0.0670285051298475</v>
-      </c>
-      <c r="AD4">
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.06701986707468779</v>
+      </c>
+      <c r="AC7">
+        <v>-0.06701986707468779</v>
+      </c>
+      <c r="AD7">
         <v>3507.4</v>
       </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
         <v>3507.4</v>
       </c>
-      <c r="AG4">
+      <c r="AG7">
         <v>-7220.1</v>
       </c>
-      <c r="AH4">
+      <c r="AH7">
         <v>0.5123208834226786</v>
       </c>
-      <c r="AI4">
+      <c r="AI7">
         <v>0.2002420671622193</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ7">
         <v>1.860179316741382</v>
       </c>
-      <c r="AK4">
+      <c r="AK7">
         <v>-1.063609445663863</v>
       </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
         <v>0</v>
       </c>
     </row>
